--- a/testdata/GodLvUpConfig.xlsx
+++ b/testdata/GodLvUpConfig.xlsx
@@ -27,13 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="56">
-  <si>
-    <t>神职升级</t>
-  </si>
-  <si>
-    <t>不需要这个内容</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="52">
   <si>
     <t xml:space="preserve">配置逻辑转 ConditionConfig </t>
   </si>
@@ -50,9 +44,6 @@
     <t>描述</t>
   </si>
   <si>
-    <t>皮肤id</t>
-  </si>
-  <si>
     <t>解锁条件，空 = 默认解锁</t>
   </si>
   <si>
@@ -77,9 +68,6 @@
     <t>desc</t>
   </si>
   <si>
-    <t>skinId</t>
-  </si>
-  <si>
     <t>lvUpConditionText</t>
   </si>
   <si>
@@ -113,7 +101,7 @@
     <t>SERVER</t>
   </si>
   <si>
-    <t>0阶鱼王</t>
+    <t>0级</t>
   </si>
   <si>
     <t>未解锁</t>
@@ -126,7 +114,7 @@
 PASS_PVE_LEVEL | levelId = 1002</t>
   </si>
   <si>
-    <t>一阶鱼王</t>
+    <t>1级</t>
   </si>
   <si>
     <t>描述 1</t>
@@ -138,7 +126,7 @@
     <t>[ 2 ]</t>
   </si>
   <si>
-    <t>二阶鱼王</t>
+    <t>2级</t>
   </si>
   <si>
     <t>描述 2</t>
@@ -157,7 +145,7 @@
     <t>[ 3,4 ]</t>
   </si>
   <si>
-    <t>三阶鱼王</t>
+    <t>3级</t>
   </si>
   <si>
     <t>描述 3</t>
@@ -176,7 +164,7 @@
     <t>[ 5 ]</t>
   </si>
   <si>
-    <t>四阶鱼王</t>
+    <t>4级</t>
   </si>
   <si>
     <t>描述 4</t>
@@ -192,7 +180,7 @@
     <t>1001,400;1002,400</t>
   </si>
   <si>
-    <t>五阶鱼王</t>
+    <t>5级</t>
   </si>
   <si>
     <t>描述 5</t>
@@ -208,7 +196,7 @@
     <t>1001,500;1002,500</t>
   </si>
   <si>
-    <t>六阶鱼王</t>
+    <t>6级</t>
   </si>
   <si>
     <t>描述 6</t>
@@ -415,18 +403,12 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="38">
+  <fills count="37">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -786,7 +768,7 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -810,16 +792,16 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="8" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="9" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="10" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -828,89 +810,89 @@
     <xf numFmtId="0" fontId="19" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
@@ -926,34 +908,31 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1514,1196 +1493,1126 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AB56"/>
+  <dimension ref="A1:AA56"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="27.3833333333333" style="1" customWidth="1"/>
     <col min="2" max="2" width="19" style="1" customWidth="1"/>
     <col min="3" max="3" width="17.625" style="1" customWidth="1"/>
     <col min="4" max="4" width="27" style="1" customWidth="1"/>
-    <col min="5" max="5" width="27.25" style="1" customWidth="1"/>
-    <col min="6" max="6" width="49" style="1" customWidth="1"/>
-    <col min="7" max="7" width="24.75" style="1" customWidth="1"/>
-    <col min="8" max="8" width="31.8416666666667" style="1" customWidth="1"/>
-    <col min="9" max="9" width="31.7416666666667" style="2" customWidth="1"/>
-    <col min="10" max="10" width="23.3666666666667" style="1" customWidth="1"/>
-    <col min="11" max="11" width="18" style="1" customWidth="1"/>
-    <col min="12" max="12" width="23.1833333333333" style="1" customWidth="1"/>
-    <col min="13" max="13" width="24.75" style="1" customWidth="1"/>
-    <col min="14" max="14" width="25" style="1" customWidth="1"/>
-    <col min="15" max="15" width="28.375" style="1" customWidth="1"/>
-    <col min="16" max="16" width="38.625" style="1" customWidth="1"/>
-    <col min="17" max="17" width="57.875" style="1" customWidth="1"/>
-    <col min="18" max="18" width="33.375" style="1" customWidth="1"/>
-    <col min="19" max="19" width="33.375" style="1" hidden="1" customWidth="1"/>
-    <col min="20" max="20" width="61.875" style="1" customWidth="1"/>
-    <col min="21" max="22" width="41" style="1" customWidth="1"/>
-    <col min="23" max="23" width="16.375" style="1" customWidth="1"/>
-    <col min="24" max="24" width="15.625" style="1" customWidth="1"/>
-    <col min="25" max="25" width="30.2583333333333" style="1" customWidth="1"/>
-    <col min="26" max="26" width="28.2583333333333" style="1" customWidth="1"/>
-    <col min="27" max="16383" width="9" style="3"/>
+    <col min="5" max="5" width="49" style="1" customWidth="1"/>
+    <col min="6" max="6" width="24.75" style="1" customWidth="1"/>
+    <col min="7" max="7" width="31.8416666666667" style="1" customWidth="1"/>
+    <col min="8" max="8" width="31.7416666666667" style="2" customWidth="1"/>
+    <col min="9" max="9" width="23.3666666666667" style="1" customWidth="1"/>
+    <col min="10" max="10" width="18" style="1" customWidth="1"/>
+    <col min="11" max="11" width="23.1833333333333" style="1" customWidth="1"/>
+    <col min="12" max="12" width="24.75" style="1" customWidth="1"/>
+    <col min="13" max="13" width="25" style="1" customWidth="1"/>
+    <col min="14" max="14" width="28.375" style="1" customWidth="1"/>
+    <col min="15" max="15" width="38.625" style="1" customWidth="1"/>
+    <col min="16" max="16" width="57.875" style="1" customWidth="1"/>
+    <col min="17" max="17" width="33.375" style="1" customWidth="1"/>
+    <col min="18" max="18" width="33.375" style="1" hidden="1" customWidth="1"/>
+    <col min="19" max="19" width="61.875" style="1" customWidth="1"/>
+    <col min="20" max="21" width="41" style="1" customWidth="1"/>
+    <col min="22" max="22" width="16.375" style="1" customWidth="1"/>
+    <col min="23" max="23" width="15.625" style="1" customWidth="1"/>
+    <col min="24" max="24" width="30.2583333333333" style="1" customWidth="1"/>
+    <col min="25" max="25" width="28.2583333333333" style="1" customWidth="1"/>
+    <col min="26" max="16382" width="9" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" ht="35" customHeight="1" spans="1:26">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
+    <row r="1" ht="35" customHeight="1" spans="1:25">
       <c r="D1" s="4"/>
       <c r="E1" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="F1" s="4"/>
+      <c r="G1" s="4"/>
+      <c r="H1" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="I1" s="7"/>
+      <c r="J1" s="8"/>
+      <c r="K1" s="8"/>
+      <c r="L1" s="8"/>
+      <c r="M1" s="5"/>
+      <c r="U1" s="9"/>
+      <c r="V1" s="9"/>
+      <c r="W1" s="9"/>
+      <c r="X1" s="9"/>
+      <c r="Y1" s="9"/>
+    </row>
+    <row r="2" spans="1:25">
+      <c r="A2" s="10"/>
+      <c r="B2" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="G1" s="4"/>
-      <c r="H1" s="4"/>
-      <c r="I1" s="7" t="s">
+      <c r="C2" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="J1" s="8"/>
-      <c r="K1" s="9"/>
-      <c r="L1" s="9"/>
-      <c r="M1" s="9"/>
-      <c r="N1" s="6"/>
-      <c r="V1" s="10"/>
-      <c r="W1" s="10"/>
-      <c r="X1" s="10"/>
-      <c r="Y1" s="10"/>
-      <c r="Z1" s="10"/>
-    </row>
-    <row r="2" spans="1:26">
-      <c r="A2" s="11"/>
-      <c r="B2" s="11" t="s">
+      <c r="D2" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="11" t="s">
+      <c r="E2" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="D2" s="11" t="s">
+      <c r="F2" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="E2" s="11" t="s">
+      <c r="G2" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="F2" s="11" t="s">
+      <c r="H2" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="G2" s="11" t="s">
+      <c r="I2" s="10"/>
+      <c r="J2" s="10"/>
+      <c r="K2" s="10"/>
+      <c r="L2" s="10"/>
+      <c r="M2" s="10"/>
+      <c r="N2" s="10"/>
+      <c r="O2" s="10"/>
+      <c r="P2" s="10"/>
+      <c r="Q2" s="10"/>
+      <c r="R2" s="10"/>
+      <c r="S2" s="10"/>
+      <c r="T2" s="10"/>
+      <c r="U2" s="10"/>
+      <c r="V2" s="10"/>
+      <c r="W2" s="10"/>
+      <c r="X2" s="10"/>
+      <c r="Y2" s="10"/>
+    </row>
+    <row r="3" spans="1:25">
+      <c r="A3" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="H2" s="11" t="s">
+      <c r="B3" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="I2" s="12" t="s">
+      <c r="C3" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="J2" s="11"/>
-      <c r="K2" s="11"/>
-      <c r="L2" s="11"/>
-      <c r="M2" s="11"/>
-      <c r="N2" s="11"/>
-      <c r="O2" s="11"/>
-      <c r="P2" s="11"/>
-      <c r="Q2" s="11"/>
-      <c r="R2" s="11"/>
-      <c r="S2" s="11"/>
-      <c r="T2" s="11"/>
-      <c r="U2" s="11"/>
-      <c r="V2" s="11"/>
-      <c r="W2" s="11"/>
-      <c r="X2" s="11"/>
-      <c r="Y2" s="11"/>
-      <c r="Z2" s="11"/>
-    </row>
-    <row r="3" spans="1:26">
-      <c r="A3" s="13" t="s">
+      <c r="D3" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="B3" s="13" t="s">
+      <c r="E3" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="C3" s="13" t="s">
+      <c r="F3" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="D3" s="13" t="s">
+      <c r="G3" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="E3" s="13" t="s">
+      <c r="H3" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="F3" s="13" t="s">
+      <c r="I3" s="12"/>
+      <c r="J3" s="12"/>
+      <c r="K3" s="12"/>
+      <c r="L3" s="12"/>
+      <c r="M3" s="12"/>
+      <c r="N3" s="12"/>
+      <c r="O3" s="12"/>
+      <c r="P3" s="12"/>
+      <c r="Q3" s="12"/>
+      <c r="R3" s="12"/>
+      <c r="S3" s="12"/>
+      <c r="T3" s="12"/>
+      <c r="U3" s="12"/>
+      <c r="V3" s="12"/>
+      <c r="W3" s="12"/>
+      <c r="X3" s="12"/>
+      <c r="Y3" s="12"/>
+    </row>
+    <row r="4" spans="1:25">
+      <c r="A4" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="G3" s="13" t="s">
+      <c r="B4" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="H3" s="13" t="s">
+      <c r="C4" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I3" s="14" t="s">
+      <c r="D4" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="E4" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="J3" s="13"/>
-      <c r="K3" s="13"/>
-      <c r="L3" s="13"/>
-      <c r="M3" s="13"/>
-      <c r="N3" s="13"/>
-      <c r="O3" s="13"/>
-      <c r="P3" s="13"/>
-      <c r="Q3" s="13"/>
-      <c r="R3" s="13"/>
-      <c r="S3" s="13"/>
-      <c r="T3" s="13"/>
-      <c r="U3" s="13"/>
-      <c r="V3" s="13"/>
-      <c r="W3" s="13"/>
-      <c r="X3" s="13"/>
-      <c r="Y3" s="13"/>
-      <c r="Z3" s="13"/>
-    </row>
-    <row r="4" spans="1:26">
-      <c r="A4" s="11" t="s">
+      <c r="F4" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="G4" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="B4" s="11" t="s">
+      <c r="H4" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="C4" s="11" t="s">
+      <c r="I4" s="10"/>
+      <c r="J4" s="10"/>
+      <c r="K4" s="10"/>
+      <c r="L4" s="10"/>
+      <c r="M4" s="10"/>
+      <c r="N4" s="10"/>
+      <c r="O4" s="10"/>
+      <c r="P4" s="10"/>
+      <c r="Q4" s="10"/>
+      <c r="R4" s="10"/>
+      <c r="S4" s="10"/>
+      <c r="T4" s="10"/>
+      <c r="U4" s="10"/>
+      <c r="V4" s="10"/>
+      <c r="W4" s="10"/>
+      <c r="X4" s="10"/>
+      <c r="Y4" s="10"/>
+    </row>
+    <row r="5" spans="1:25">
+      <c r="A5" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="D4" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="E4" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="F4" s="11" t="s">
+      <c r="B5" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="C5" s="12"/>
+      <c r="D5" s="12"/>
+      <c r="E5" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="F5" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="G5" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="H5" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="I5" s="12"/>
+      <c r="J5" s="12"/>
+      <c r="K5" s="12"/>
+      <c r="L5" s="12"/>
+      <c r="M5" s="12"/>
+      <c r="N5" s="12"/>
+      <c r="O5" s="12"/>
+      <c r="P5" s="12"/>
+      <c r="Q5" s="12"/>
+      <c r="R5" s="12"/>
+      <c r="S5" s="12"/>
+      <c r="T5" s="12"/>
+      <c r="U5" s="12"/>
+      <c r="V5" s="12"/>
+      <c r="W5" s="12"/>
+      <c r="X5" s="12"/>
+      <c r="Y5" s="12"/>
+    </row>
+    <row r="6" ht="86.25" spans="1:25">
+      <c r="B6" s="14">
+        <v>0</v>
+      </c>
+      <c r="C6" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="G4" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="H4" s="11" t="s">
+      <c r="D6" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="I4" s="12" t="s">
+      <c r="E6" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="J4" s="11"/>
-      <c r="K4" s="11"/>
-      <c r="L4" s="11"/>
-      <c r="M4" s="11"/>
-      <c r="N4" s="11"/>
-      <c r="O4" s="11"/>
-      <c r="P4" s="11"/>
-      <c r="Q4" s="11"/>
-      <c r="R4" s="11"/>
-      <c r="S4" s="11"/>
-      <c r="T4" s="11"/>
-      <c r="U4" s="11"/>
-      <c r="V4" s="11"/>
-      <c r="W4" s="11"/>
-      <c r="X4" s="11"/>
-      <c r="Y4" s="11"/>
-      <c r="Z4" s="11"/>
-    </row>
-    <row r="5" spans="1:26">
-      <c r="A5" s="13" t="s">
+      <c r="F6" s="17"/>
+      <c r="G6" s="14"/>
+      <c r="H6" s="18"/>
+      <c r="I6" s="14"/>
+      <c r="J6" s="14"/>
+      <c r="K6" s="14"/>
+      <c r="L6" s="14"/>
+      <c r="M6" s="14"/>
+      <c r="N6" s="15"/>
+      <c r="O6" s="15"/>
+      <c r="P6" s="15"/>
+      <c r="Q6" s="15"/>
+      <c r="S6" s="15"/>
+      <c r="T6" s="15"/>
+    </row>
+    <row r="7" ht="86.25" spans="1:25">
+      <c r="B7" s="14">
+        <v>1</v>
+      </c>
+      <c r="C7" s="14" t="s">
         <v>27</v>
       </c>
-      <c r="B5" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="C5" s="13"/>
-      <c r="D5" s="13"/>
-      <c r="E5" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="F5" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="G5" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="H5" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="I5" s="14" t="s">
-        <v>20</v>
-      </c>
-      <c r="J5" s="13"/>
-      <c r="K5" s="13"/>
-      <c r="L5" s="13"/>
-      <c r="M5" s="13"/>
-      <c r="N5" s="13"/>
-      <c r="O5" s="13"/>
-      <c r="P5" s="13"/>
-      <c r="Q5" s="13"/>
-      <c r="R5" s="13"/>
-      <c r="S5" s="13"/>
-      <c r="T5" s="13"/>
-      <c r="U5" s="13"/>
-      <c r="V5" s="13"/>
-      <c r="W5" s="13"/>
-      <c r="X5" s="13"/>
-      <c r="Y5" s="13"/>
-      <c r="Z5" s="13"/>
-    </row>
-    <row r="6" ht="86.25" spans="1:26">
-      <c r="B6" s="15">
-        <v>0</v>
-      </c>
-      <c r="C6" s="15" t="s">
+      <c r="D7" s="15" t="s">
         <v>28</v>
       </c>
-      <c r="D6" s="16" t="s">
+      <c r="E7" s="16" t="s">
+        <v>26</v>
+      </c>
+      <c r="F7" s="17" t="s">
         <v>29</v>
       </c>
-      <c r="E6" s="16"/>
-      <c r="F6" s="17" t="s">
+      <c r="G7" s="14">
+        <v>10</v>
+      </c>
+      <c r="H7" s="18" t="s">
         <v>30</v>
       </c>
-      <c r="G6" s="18"/>
-      <c r="H6" s="15"/>
-      <c r="I6" s="19"/>
-      <c r="J6" s="15"/>
-      <c r="K6" s="15"/>
-      <c r="L6" s="15"/>
-      <c r="M6" s="15"/>
-      <c r="N6" s="15"/>
-      <c r="O6" s="16"/>
-      <c r="P6" s="16"/>
-      <c r="Q6" s="16"/>
-      <c r="R6" s="16"/>
-      <c r="T6" s="16"/>
-      <c r="U6" s="16"/>
-    </row>
-    <row r="7" ht="86.25" spans="1:26">
-      <c r="B7" s="15">
-        <v>1</v>
-      </c>
-      <c r="C7" s="15" t="s">
+      <c r="I7" s="14"/>
+      <c r="J7" s="14"/>
+      <c r="K7" s="14"/>
+      <c r="L7" s="14"/>
+      <c r="M7" s="14"/>
+      <c r="N7" s="15"/>
+      <c r="O7" s="15"/>
+      <c r="P7" s="15"/>
+      <c r="Q7" s="15"/>
+      <c r="S7" s="15"/>
+      <c r="T7" s="15"/>
+    </row>
+    <row r="8" ht="86.25" spans="1:25">
+      <c r="B8" s="14">
+        <v>2</v>
+      </c>
+      <c r="C8" s="14" t="s">
         <v>31</v>
       </c>
-      <c r="D7" s="16" t="s">
+      <c r="D8" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="E7" s="16"/>
-      <c r="F7" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="G7" s="18" t="s">
+      <c r="E8" s="16" t="s">
         <v>33</v>
       </c>
-      <c r="H7" s="15">
+      <c r="F8" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="G8" s="14">
         <v>10</v>
       </c>
-      <c r="I7" s="19" t="s">
-        <v>34</v>
-      </c>
-      <c r="J7" s="15"/>
-      <c r="K7" s="15"/>
-      <c r="L7" s="15"/>
-      <c r="M7" s="15"/>
-      <c r="N7" s="15"/>
-      <c r="O7" s="16"/>
-      <c r="P7" s="16"/>
-      <c r="Q7" s="16"/>
-      <c r="R7" s="16"/>
-      <c r="T7" s="16"/>
-      <c r="U7" s="16"/>
-    </row>
-    <row r="8" ht="86.25" spans="1:26">
-      <c r="B8" s="15">
-        <v>2</v>
-      </c>
-      <c r="C8" s="15" t="s">
+      <c r="H8" s="18" t="s">
         <v>35</v>
       </c>
-      <c r="D8" s="16" t="s">
+      <c r="I8" s="14"/>
+      <c r="J8" s="14"/>
+      <c r="K8" s="14"/>
+      <c r="L8" s="14"/>
+      <c r="M8" s="14"/>
+      <c r="N8" s="15"/>
+      <c r="O8" s="15"/>
+      <c r="P8" s="15"/>
+      <c r="Q8" s="15"/>
+      <c r="S8" s="15"/>
+      <c r="T8" s="15"/>
+    </row>
+    <row r="9" ht="86.25" spans="1:25">
+      <c r="B9" s="14">
+        <v>3</v>
+      </c>
+      <c r="C9" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="E8" s="16"/>
-      <c r="F8" s="17" t="s">
+      <c r="D9" s="15" t="s">
         <v>37</v>
       </c>
-      <c r="G8" s="18" t="s">
+      <c r="E9" s="16" t="s">
         <v>38</v>
       </c>
-      <c r="H8" s="15">
+      <c r="F9" s="17" t="s">
+        <v>39</v>
+      </c>
+      <c r="G9" s="14">
         <v>10</v>
       </c>
-      <c r="I8" s="19" t="s">
-        <v>39</v>
-      </c>
-      <c r="J8" s="15"/>
-      <c r="K8" s="15"/>
-      <c r="L8" s="15"/>
-      <c r="M8" s="15"/>
-      <c r="N8" s="15"/>
-      <c r="O8" s="16"/>
-      <c r="P8" s="16"/>
-      <c r="Q8" s="16"/>
-      <c r="R8" s="16"/>
-      <c r="T8" s="16"/>
-      <c r="U8" s="16"/>
-    </row>
-    <row r="9" ht="86.25" spans="1:26">
-      <c r="B9" s="15">
-        <v>3</v>
-      </c>
-      <c r="C9" s="15" t="s">
+      <c r="H9" s="18" t="s">
         <v>40</v>
       </c>
-      <c r="D9" s="16" t="s">
+      <c r="I9" s="14"/>
+      <c r="J9" s="14"/>
+      <c r="K9" s="14"/>
+      <c r="L9" s="14"/>
+      <c r="M9" s="14"/>
+      <c r="N9" s="15"/>
+      <c r="O9" s="15"/>
+      <c r="P9" s="15"/>
+      <c r="Q9" s="15"/>
+      <c r="S9" s="15"/>
+      <c r="T9" s="15"/>
+      <c r="U9" s="15"/>
+    </row>
+    <row r="10" ht="86.25" spans="1:25">
+      <c r="B10" s="14">
+        <v>4</v>
+      </c>
+      <c r="C10" s="14" t="s">
         <v>41</v>
       </c>
-      <c r="E9" s="16"/>
-      <c r="F9" s="17" t="s">
+      <c r="D10" s="15" t="s">
         <v>42</v>
       </c>
-      <c r="G9" s="18" t="s">
+      <c r="E10" s="16" t="s">
         <v>43</v>
       </c>
-      <c r="H9" s="15">
+      <c r="F10" s="17" t="s">
+        <v>44</v>
+      </c>
+      <c r="G10" s="14">
         <v>10</v>
       </c>
-      <c r="I9" s="19" t="s">
-        <v>44</v>
-      </c>
-      <c r="J9" s="15"/>
-      <c r="K9" s="15"/>
-      <c r="L9" s="15"/>
-      <c r="M9" s="15"/>
-      <c r="N9" s="15"/>
-      <c r="O9" s="16"/>
-      <c r="P9" s="16"/>
-      <c r="Q9" s="16"/>
-      <c r="R9" s="16"/>
-      <c r="T9" s="16"/>
-      <c r="U9" s="16"/>
-      <c r="V9" s="16"/>
-    </row>
-    <row r="10" ht="86.25" spans="1:26">
-      <c r="B10" s="15">
-        <v>4</v>
-      </c>
-      <c r="C10" s="15" t="s">
+      <c r="H10" s="18"/>
+      <c r="I10" s="14"/>
+      <c r="J10" s="14"/>
+      <c r="K10" s="14"/>
+      <c r="L10" s="14"/>
+      <c r="M10" s="14"/>
+      <c r="N10" s="15"/>
+      <c r="O10" s="15"/>
+      <c r="P10" s="15"/>
+      <c r="Q10" s="15"/>
+      <c r="S10" s="15"/>
+      <c r="T10" s="15"/>
+      <c r="U10" s="15"/>
+    </row>
+    <row r="11" ht="86.25" spans="1:25">
+      <c r="B11" s="14">
+        <v>5</v>
+      </c>
+      <c r="C11" s="14" t="s">
         <v>45</v>
       </c>
-      <c r="D10" s="16" t="s">
+      <c r="D11" s="15" t="s">
         <v>46</v>
       </c>
-      <c r="E10" s="16"/>
-      <c r="F10" s="17" t="s">
+      <c r="E11" s="16" t="s">
         <v>47</v>
       </c>
-      <c r="G10" s="18" t="s">
+      <c r="F11" s="17" t="s">
         <v>48</v>
       </c>
-      <c r="H10" s="15">
+      <c r="G11" s="14">
         <v>10</v>
       </c>
-      <c r="I10" s="19"/>
-      <c r="J10" s="15"/>
-      <c r="K10" s="15"/>
-      <c r="L10" s="15"/>
-      <c r="M10" s="15"/>
-      <c r="N10" s="15"/>
-      <c r="O10" s="16"/>
-      <c r="P10" s="16"/>
-      <c r="Q10" s="16"/>
-      <c r="R10" s="16"/>
-      <c r="T10" s="16"/>
-      <c r="U10" s="16"/>
-      <c r="V10" s="16"/>
-    </row>
-    <row r="11" ht="86.25" spans="1:26">
-      <c r="B11" s="15">
-        <v>5</v>
-      </c>
-      <c r="C11" s="15" t="s">
+      <c r="H11" s="18"/>
+      <c r="I11" s="14"/>
+      <c r="J11" s="14"/>
+      <c r="K11" s="14"/>
+      <c r="L11" s="14"/>
+      <c r="M11" s="14"/>
+      <c r="N11" s="15"/>
+    </row>
+    <row r="12" ht="86.25" spans="1:25">
+      <c r="B12" s="14">
+        <v>6</v>
+      </c>
+      <c r="C12" s="14" t="s">
         <v>49</v>
       </c>
-      <c r="D11" s="16" t="s">
+      <c r="D12" s="15" t="s">
         <v>50</v>
       </c>
-      <c r="E11" s="16"/>
-      <c r="F11" s="17" t="s">
+      <c r="E12" s="16" t="s">
         <v>51</v>
       </c>
-      <c r="G11" s="18" t="s">
-        <v>52</v>
-      </c>
-      <c r="H11" s="15">
+      <c r="F12" s="14"/>
+      <c r="G12" s="14">
         <v>10</v>
       </c>
-      <c r="I11" s="19"/>
-      <c r="J11" s="15"/>
-      <c r="K11" s="15"/>
-      <c r="L11" s="15"/>
-      <c r="M11" s="15"/>
-      <c r="N11" s="15"/>
-      <c r="O11" s="16"/>
-    </row>
-    <row r="12" ht="86.25" spans="1:26">
-      <c r="B12" s="15">
-        <v>6</v>
-      </c>
-      <c r="C12" s="15" t="s">
-        <v>53</v>
-      </c>
-      <c r="D12" s="16" t="s">
-        <v>54</v>
-      </c>
-      <c r="E12" s="16"/>
-      <c r="F12" s="17" t="s">
-        <v>55</v>
-      </c>
-      <c r="G12" s="15"/>
-      <c r="H12" s="15">
-        <v>10</v>
-      </c>
-      <c r="I12" s="19"/>
-      <c r="J12" s="15"/>
-      <c r="K12" s="15"/>
-      <c r="L12" s="15"/>
-      <c r="M12" s="15"/>
+      <c r="H12" s="18"/>
+      <c r="I12" s="14"/>
+      <c r="J12" s="14"/>
+      <c r="K12" s="14"/>
+      <c r="L12" s="14"/>
+      <c r="M12" s="14"/>
       <c r="N12" s="15"/>
-      <c r="O12" s="16"/>
-    </row>
-    <row r="13" ht="17.25" spans="1:26">
-      <c r="B13" s="15"/>
-      <c r="C13" s="15"/>
-      <c r="D13" s="16"/>
-      <c r="E13" s="16"/>
-      <c r="F13" s="16"/>
-      <c r="G13" s="15"/>
-      <c r="H13" s="15"/>
-      <c r="I13" s="19"/>
-      <c r="J13" s="15"/>
-      <c r="K13" s="15"/>
-      <c r="L13" s="15"/>
-      <c r="M13" s="15"/>
+    </row>
+    <row r="13" ht="17.25" spans="1:25">
+      <c r="B13" s="14"/>
+      <c r="C13" s="14"/>
+      <c r="D13" s="15"/>
+      <c r="E13" s="15"/>
+      <c r="F13" s="14"/>
+      <c r="G13" s="14"/>
+      <c r="H13" s="18"/>
+      <c r="I13" s="14"/>
+      <c r="J13" s="14"/>
+      <c r="K13" s="14"/>
+      <c r="L13" s="14"/>
+      <c r="M13" s="14"/>
       <c r="N13" s="15"/>
-      <c r="O13" s="16"/>
-    </row>
-    <row r="14" ht="17.25" spans="1:26">
-      <c r="B14" s="15"/>
-      <c r="C14" s="15"/>
-      <c r="D14" s="16"/>
-      <c r="E14" s="16"/>
-      <c r="F14" s="16"/>
-      <c r="G14" s="15"/>
-      <c r="H14" s="15"/>
-      <c r="I14" s="19"/>
-      <c r="J14" s="15"/>
-      <c r="K14" s="15"/>
-      <c r="L14" s="15"/>
-      <c r="M14" s="15"/>
+    </row>
+    <row r="14" ht="17.25" spans="1:25">
+      <c r="B14" s="14"/>
+      <c r="C14" s="14"/>
+      <c r="D14" s="15"/>
+      <c r="E14" s="15"/>
+      <c r="F14" s="14"/>
+      <c r="G14" s="14"/>
+      <c r="H14" s="18"/>
+      <c r="I14" s="14"/>
+      <c r="J14" s="14"/>
+      <c r="K14" s="14"/>
+      <c r="L14" s="14"/>
+      <c r="M14" s="14"/>
       <c r="N14" s="15"/>
-      <c r="O14" s="16"/>
-    </row>
-    <row r="15" ht="17.25" spans="1:26">
-      <c r="B15" s="15"/>
-      <c r="C15" s="15"/>
-      <c r="D15" s="16"/>
-      <c r="E15" s="16"/>
-      <c r="F15" s="16"/>
-      <c r="G15" s="15"/>
-      <c r="H15" s="15"/>
-      <c r="I15" s="19"/>
-      <c r="J15" s="15"/>
-      <c r="K15" s="15"/>
-      <c r="L15" s="15"/>
-      <c r="M15" s="15"/>
+    </row>
+    <row r="15" ht="17.25" spans="1:25">
+      <c r="B15" s="14"/>
+      <c r="C15" s="14"/>
+      <c r="D15" s="15"/>
+      <c r="E15" s="15"/>
+      <c r="F15" s="14"/>
+      <c r="G15" s="14"/>
+      <c r="H15" s="18"/>
+      <c r="I15" s="14"/>
+      <c r="J15" s="14"/>
+      <c r="K15" s="14"/>
+      <c r="L15" s="14"/>
+      <c r="M15" s="14"/>
       <c r="N15" s="15"/>
-      <c r="O15" s="16"/>
-    </row>
-    <row r="16" ht="17.25" spans="1:26">
-      <c r="B16" s="15"/>
-      <c r="C16" s="15"/>
-      <c r="D16" s="16"/>
-      <c r="E16" s="16"/>
-      <c r="F16" s="16"/>
-      <c r="G16" s="15"/>
-      <c r="H16" s="15"/>
-      <c r="I16" s="19"/>
-      <c r="J16" s="15"/>
-      <c r="K16" s="15"/>
-      <c r="L16" s="15"/>
-      <c r="M16" s="15"/>
+    </row>
+    <row r="16" ht="17.25" spans="1:25">
+      <c r="B16" s="14"/>
+      <c r="C16" s="14"/>
+      <c r="D16" s="15"/>
+      <c r="E16" s="15"/>
+      <c r="F16" s="14"/>
+      <c r="G16" s="14"/>
+      <c r="H16" s="18"/>
+      <c r="I16" s="14"/>
+      <c r="J16" s="14"/>
+      <c r="K16" s="14"/>
+      <c r="L16" s="14"/>
+      <c r="M16" s="14"/>
       <c r="N16" s="15"/>
-      <c r="O16" s="16"/>
-    </row>
-    <row r="17" ht="17.25" spans="2:28">
-      <c r="B17" s="15"/>
-      <c r="C17" s="15"/>
-      <c r="D17" s="16"/>
-      <c r="E17" s="16"/>
-      <c r="F17" s="16"/>
-      <c r="G17" s="15"/>
-      <c r="H17" s="15"/>
-      <c r="I17" s="19"/>
-      <c r="J17" s="15"/>
-      <c r="K17" s="15"/>
-      <c r="L17" s="15"/>
-      <c r="M17" s="15"/>
+    </row>
+    <row r="17" ht="17.25" spans="2:27">
+      <c r="B17" s="14"/>
+      <c r="C17" s="14"/>
+      <c r="D17" s="15"/>
+      <c r="E17" s="15"/>
+      <c r="F17" s="14"/>
+      <c r="G17" s="14"/>
+      <c r="H17" s="18"/>
+      <c r="I17" s="14"/>
+      <c r="J17" s="14"/>
+      <c r="K17" s="14"/>
+      <c r="L17" s="14"/>
+      <c r="M17" s="14"/>
       <c r="N17" s="15"/>
-      <c r="O17" s="16"/>
-    </row>
-    <row r="18" ht="17.25" spans="2:28">
-      <c r="B18" s="15"/>
-      <c r="C18" s="15"/>
-      <c r="D18" s="16"/>
-      <c r="E18" s="16"/>
-      <c r="F18" s="16"/>
-      <c r="G18" s="15"/>
-      <c r="H18" s="15"/>
-      <c r="I18" s="19"/>
-      <c r="J18" s="15"/>
-      <c r="K18" s="15"/>
-      <c r="L18" s="15"/>
-      <c r="M18" s="15"/>
+    </row>
+    <row r="18" ht="17.25" spans="2:27">
+      <c r="B18" s="14"/>
+      <c r="C18" s="14"/>
+      <c r="D18" s="15"/>
+      <c r="E18" s="15"/>
+      <c r="F18" s="14"/>
+      <c r="G18" s="14"/>
+      <c r="H18" s="18"/>
+      <c r="I18" s="14"/>
+      <c r="J18" s="14"/>
+      <c r="K18" s="14"/>
+      <c r="L18" s="14"/>
+      <c r="M18" s="14"/>
       <c r="N18" s="15"/>
-      <c r="O18" s="16"/>
-    </row>
-    <row r="19" ht="17.25" spans="2:28">
-      <c r="B19" s="15"/>
-      <c r="C19" s="15"/>
-      <c r="D19" s="16"/>
-      <c r="E19" s="16"/>
-      <c r="F19" s="16"/>
-      <c r="G19" s="15"/>
-      <c r="H19" s="15"/>
-      <c r="I19" s="19"/>
-      <c r="J19" s="15"/>
-      <c r="K19" s="15"/>
-      <c r="L19" s="15"/>
-      <c r="M19" s="15"/>
+    </row>
+    <row r="19" ht="17.25" spans="2:27">
+      <c r="B19" s="14"/>
+      <c r="C19" s="14"/>
+      <c r="D19" s="15"/>
+      <c r="E19" s="15"/>
+      <c r="F19" s="14"/>
+      <c r="G19" s="14"/>
+      <c r="H19" s="18"/>
+      <c r="I19" s="14"/>
+      <c r="J19" s="14"/>
+      <c r="K19" s="14"/>
+      <c r="L19" s="14"/>
+      <c r="M19" s="14"/>
       <c r="N19" s="15"/>
-      <c r="O19" s="16"/>
-      <c r="P19" s="20"/>
-      <c r="Q19" s="20"/>
-      <c r="R19" s="20"/>
-      <c r="S19" s="20"/>
-      <c r="T19" s="20"/>
-      <c r="U19" s="20"/>
-      <c r="V19" s="20"/>
-      <c r="W19" s="20"/>
-      <c r="X19" s="20"/>
-      <c r="Y19" s="20"/>
-      <c r="Z19" s="20"/>
+      <c r="O19" s="19"/>
+      <c r="P19" s="19"/>
+      <c r="Q19" s="19"/>
+      <c r="R19" s="19"/>
+      <c r="S19" s="19"/>
+      <c r="T19" s="19"/>
+      <c r="U19" s="19"/>
+      <c r="V19" s="19"/>
+      <c r="W19" s="19"/>
+      <c r="X19" s="19"/>
+      <c r="Y19" s="19"/>
+      <c r="Z19"/>
       <c r="AA19"/>
-      <c r="AB19"/>
-    </row>
-    <row r="20" ht="17.25" spans="2:28">
-      <c r="B20" s="15"/>
-      <c r="C20" s="15"/>
-      <c r="D20" s="16"/>
-      <c r="E20" s="16"/>
-      <c r="F20" s="16"/>
-      <c r="G20" s="15"/>
-      <c r="H20" s="15"/>
-      <c r="I20" s="19"/>
-      <c r="J20" s="15"/>
-      <c r="K20" s="15"/>
-      <c r="L20" s="15"/>
-      <c r="M20" s="15"/>
+    </row>
+    <row r="20" ht="17.25" spans="2:27">
+      <c r="B20" s="14"/>
+      <c r="C20" s="14"/>
+      <c r="D20" s="15"/>
+      <c r="E20" s="15"/>
+      <c r="F20" s="14"/>
+      <c r="G20" s="14"/>
+      <c r="H20" s="18"/>
+      <c r="I20" s="14"/>
+      <c r="J20" s="14"/>
+      <c r="K20" s="14"/>
+      <c r="L20" s="14"/>
+      <c r="M20" s="14"/>
       <c r="N20" s="15"/>
-      <c r="O20" s="16"/>
-    </row>
-    <row r="21" ht="17.25" spans="2:28">
-      <c r="B21" s="15"/>
-      <c r="C21" s="15"/>
-      <c r="D21" s="16"/>
-      <c r="E21" s="16"/>
-      <c r="F21" s="16"/>
-      <c r="G21" s="15"/>
-      <c r="H21" s="15"/>
-      <c r="I21" s="19"/>
-      <c r="J21" s="15"/>
-      <c r="K21" s="15"/>
-      <c r="L21" s="15"/>
-      <c r="M21" s="15"/>
+    </row>
+    <row r="21" ht="17.25" spans="2:27">
+      <c r="B21" s="14"/>
+      <c r="C21" s="14"/>
+      <c r="D21" s="15"/>
+      <c r="E21" s="15"/>
+      <c r="F21" s="14"/>
+      <c r="G21" s="14"/>
+      <c r="H21" s="18"/>
+      <c r="I21" s="14"/>
+      <c r="J21" s="14"/>
+      <c r="K21" s="14"/>
+      <c r="L21" s="14"/>
+      <c r="M21" s="14"/>
       <c r="N21" s="15"/>
-      <c r="O21" s="16"/>
-    </row>
-    <row r="22" ht="17.25" spans="2:28">
-      <c r="B22" s="15"/>
-      <c r="C22" s="15"/>
-      <c r="D22" s="16"/>
-      <c r="E22" s="16"/>
-      <c r="F22" s="16"/>
-      <c r="G22" s="15"/>
-      <c r="H22" s="15"/>
-      <c r="I22" s="19"/>
-      <c r="J22" s="15"/>
-      <c r="K22" s="15"/>
-      <c r="L22" s="15"/>
-      <c r="M22" s="15"/>
+    </row>
+    <row r="22" ht="17.25" spans="2:27">
+      <c r="B22" s="14"/>
+      <c r="C22" s="14"/>
+      <c r="D22" s="15"/>
+      <c r="E22" s="15"/>
+      <c r="F22" s="14"/>
+      <c r="G22" s="14"/>
+      <c r="H22" s="18"/>
+      <c r="I22" s="14"/>
+      <c r="J22" s="14"/>
+      <c r="K22" s="14"/>
+      <c r="L22" s="14"/>
+      <c r="M22" s="14"/>
       <c r="N22" s="15"/>
-      <c r="O22" s="16"/>
-    </row>
-    <row r="23" ht="17.25" spans="2:28">
-      <c r="B23" s="15"/>
-      <c r="C23" s="15"/>
-      <c r="D23" s="16"/>
-      <c r="E23" s="16"/>
-      <c r="F23" s="16"/>
-      <c r="G23" s="15"/>
-      <c r="H23" s="15"/>
-      <c r="I23" s="19"/>
-      <c r="J23" s="15"/>
-      <c r="K23" s="15"/>
-      <c r="L23" s="15"/>
-      <c r="M23" s="15"/>
+    </row>
+    <row r="23" ht="17.25" spans="2:27">
+      <c r="B23" s="14"/>
+      <c r="C23" s="14"/>
+      <c r="D23" s="15"/>
+      <c r="E23" s="15"/>
+      <c r="F23" s="14"/>
+      <c r="G23" s="14"/>
+      <c r="H23" s="18"/>
+      <c r="I23" s="14"/>
+      <c r="J23" s="14"/>
+      <c r="K23" s="14"/>
+      <c r="L23" s="14"/>
+      <c r="M23" s="14"/>
       <c r="N23" s="15"/>
-      <c r="O23" s="16"/>
-    </row>
-    <row r="24" ht="17.25" spans="2:28">
-      <c r="B24" s="15"/>
-      <c r="C24" s="15"/>
-      <c r="D24" s="16"/>
-      <c r="E24" s="16"/>
-      <c r="F24" s="16"/>
-      <c r="G24" s="15"/>
-      <c r="H24" s="15"/>
-      <c r="I24" s="19"/>
-      <c r="J24" s="15"/>
-      <c r="K24" s="15"/>
-      <c r="L24" s="15"/>
-      <c r="M24" s="15"/>
+    </row>
+    <row r="24" ht="17.25" spans="2:27">
+      <c r="B24" s="14"/>
+      <c r="C24" s="14"/>
+      <c r="D24" s="15"/>
+      <c r="E24" s="15"/>
+      <c r="F24" s="14"/>
+      <c r="G24" s="14"/>
+      <c r="H24" s="18"/>
+      <c r="I24" s="14"/>
+      <c r="J24" s="14"/>
+      <c r="K24" s="14"/>
+      <c r="L24" s="14"/>
+      <c r="M24" s="14"/>
       <c r="N24" s="15"/>
-      <c r="O24" s="16"/>
-    </row>
-    <row r="25" ht="17.25" spans="2:28">
-      <c r="B25" s="15"/>
-      <c r="C25" s="15"/>
-      <c r="D25" s="16"/>
-      <c r="E25" s="16"/>
-      <c r="F25" s="16"/>
-      <c r="G25" s="15"/>
-      <c r="H25" s="15"/>
-      <c r="I25" s="19"/>
-      <c r="J25" s="15"/>
-      <c r="K25" s="15"/>
-      <c r="L25" s="15"/>
-      <c r="M25" s="15"/>
+    </row>
+    <row r="25" ht="17.25" spans="2:27">
+      <c r="B25" s="14"/>
+      <c r="C25" s="14"/>
+      <c r="D25" s="15"/>
+      <c r="E25" s="15"/>
+      <c r="F25" s="14"/>
+      <c r="G25" s="14"/>
+      <c r="H25" s="18"/>
+      <c r="I25" s="14"/>
+      <c r="J25" s="14"/>
+      <c r="K25" s="14"/>
+      <c r="L25" s="14"/>
+      <c r="M25" s="14"/>
       <c r="N25" s="15"/>
-      <c r="O25" s="16"/>
-    </row>
-    <row r="26" ht="17.25" spans="2:28">
-      <c r="B26" s="15"/>
-      <c r="C26" s="15"/>
-      <c r="D26" s="16"/>
-      <c r="E26" s="16"/>
-      <c r="F26" s="16"/>
-      <c r="G26" s="15"/>
-      <c r="H26" s="15"/>
-      <c r="I26" s="19"/>
-      <c r="J26" s="15"/>
-      <c r="K26" s="15"/>
-      <c r="L26" s="15"/>
-      <c r="M26" s="15"/>
+    </row>
+    <row r="26" ht="17.25" spans="2:27">
+      <c r="B26" s="14"/>
+      <c r="C26" s="14"/>
+      <c r="D26" s="15"/>
+      <c r="E26" s="15"/>
+      <c r="F26" s="14"/>
+      <c r="G26" s="14"/>
+      <c r="H26" s="18"/>
+      <c r="I26" s="14"/>
+      <c r="J26" s="14"/>
+      <c r="K26" s="14"/>
+      <c r="L26" s="14"/>
+      <c r="M26" s="14"/>
       <c r="N26" s="15"/>
-      <c r="O26" s="16"/>
-    </row>
-    <row r="27" ht="17.25" spans="2:28">
-      <c r="B27" s="15"/>
-      <c r="C27" s="15"/>
-      <c r="D27" s="16"/>
-      <c r="E27" s="16"/>
-      <c r="F27" s="16"/>
-      <c r="G27" s="15"/>
-      <c r="H27" s="15"/>
-      <c r="I27" s="19"/>
-      <c r="J27" s="15"/>
-      <c r="K27" s="15"/>
-      <c r="L27" s="15"/>
-      <c r="M27" s="15"/>
+    </row>
+    <row r="27" ht="17.25" spans="2:27">
+      <c r="B27" s="14"/>
+      <c r="C27" s="14"/>
+      <c r="D27" s="15"/>
+      <c r="E27" s="15"/>
+      <c r="F27" s="14"/>
+      <c r="G27" s="14"/>
+      <c r="H27" s="18"/>
+      <c r="I27" s="14"/>
+      <c r="J27" s="14"/>
+      <c r="K27" s="14"/>
+      <c r="L27" s="14"/>
+      <c r="M27" s="14"/>
       <c r="N27" s="15"/>
-      <c r="O27" s="16"/>
-    </row>
-    <row r="28" ht="17.25" spans="2:28">
-      <c r="B28" s="15"/>
-      <c r="C28" s="15"/>
-      <c r="D28" s="16"/>
-      <c r="E28" s="16"/>
-      <c r="F28" s="16"/>
-      <c r="G28" s="15"/>
-      <c r="H28" s="15"/>
-      <c r="I28" s="19"/>
-      <c r="J28" s="15"/>
-      <c r="K28" s="15"/>
-      <c r="L28" s="15"/>
-      <c r="M28" s="15"/>
+    </row>
+    <row r="28" ht="17.25" spans="2:27">
+      <c r="B28" s="14"/>
+      <c r="C28" s="14"/>
+      <c r="D28" s="15"/>
+      <c r="E28" s="15"/>
+      <c r="F28" s="14"/>
+      <c r="G28" s="14"/>
+      <c r="H28" s="18"/>
+      <c r="I28" s="14"/>
+      <c r="J28" s="14"/>
+      <c r="K28" s="14"/>
+      <c r="L28" s="14"/>
+      <c r="M28" s="14"/>
       <c r="N28" s="15"/>
-      <c r="O28" s="16"/>
-    </row>
-    <row r="29" ht="17.25" spans="2:28">
-      <c r="B29" s="15"/>
-      <c r="C29" s="15"/>
-      <c r="D29" s="16"/>
-      <c r="E29" s="16"/>
-      <c r="F29" s="16"/>
-      <c r="G29" s="15"/>
-      <c r="H29" s="15"/>
-      <c r="I29" s="19"/>
-      <c r="J29" s="15"/>
-      <c r="K29" s="15"/>
-      <c r="L29" s="15"/>
-      <c r="M29" s="15"/>
+    </row>
+    <row r="29" ht="17.25" spans="2:27">
+      <c r="B29" s="14"/>
+      <c r="C29" s="14"/>
+      <c r="D29" s="15"/>
+      <c r="E29" s="15"/>
+      <c r="F29" s="14"/>
+      <c r="G29" s="14"/>
+      <c r="H29" s="18"/>
+      <c r="I29" s="14"/>
+      <c r="J29" s="14"/>
+      <c r="K29" s="14"/>
+      <c r="L29" s="14"/>
+      <c r="M29" s="14"/>
       <c r="N29" s="15"/>
-      <c r="O29" s="16"/>
-    </row>
-    <row r="30" ht="17.25" spans="2:28">
-      <c r="B30" s="15"/>
-      <c r="C30" s="15"/>
-      <c r="D30" s="16"/>
-      <c r="E30" s="16"/>
-      <c r="F30" s="16"/>
-      <c r="G30" s="15"/>
-      <c r="H30" s="15"/>
-      <c r="I30" s="19"/>
-      <c r="J30" s="15"/>
-      <c r="K30" s="15"/>
-      <c r="L30" s="15"/>
-      <c r="M30" s="15"/>
+    </row>
+    <row r="30" ht="17.25" spans="2:27">
+      <c r="B30" s="14"/>
+      <c r="C30" s="14"/>
+      <c r="D30" s="15"/>
+      <c r="E30" s="15"/>
+      <c r="F30" s="14"/>
+      <c r="G30" s="14"/>
+      <c r="H30" s="18"/>
+      <c r="I30" s="14"/>
+      <c r="J30" s="14"/>
+      <c r="K30" s="14"/>
+      <c r="L30" s="14"/>
+      <c r="M30" s="14"/>
       <c r="N30" s="15"/>
-      <c r="O30" s="16"/>
-    </row>
-    <row r="31" ht="17.25" spans="2:28">
-      <c r="B31" s="15"/>
-      <c r="C31" s="15"/>
-      <c r="D31" s="16"/>
-      <c r="E31" s="16"/>
-      <c r="F31" s="16"/>
-      <c r="G31" s="15"/>
-      <c r="H31" s="15"/>
-      <c r="I31" s="19"/>
-      <c r="J31" s="15"/>
-      <c r="K31" s="15"/>
-      <c r="L31" s="15"/>
-      <c r="M31" s="15"/>
+    </row>
+    <row r="31" ht="17.25" spans="2:27">
+      <c r="B31" s="14"/>
+      <c r="C31" s="14"/>
+      <c r="D31" s="15"/>
+      <c r="E31" s="15"/>
+      <c r="F31" s="14"/>
+      <c r="G31" s="14"/>
+      <c r="H31" s="18"/>
+      <c r="I31" s="14"/>
+      <c r="J31" s="14"/>
+      <c r="K31" s="14"/>
+      <c r="L31" s="14"/>
+      <c r="M31" s="14"/>
       <c r="N31" s="15"/>
-      <c r="O31" s="16"/>
-    </row>
-    <row r="32" ht="17.25" spans="2:28">
-      <c r="B32" s="15"/>
-      <c r="C32" s="15"/>
-      <c r="D32" s="16"/>
-      <c r="E32" s="16"/>
-      <c r="F32" s="16"/>
-      <c r="G32" s="15"/>
-      <c r="H32" s="15"/>
-      <c r="I32" s="19"/>
-      <c r="J32" s="15"/>
-      <c r="K32" s="15"/>
-      <c r="L32" s="15"/>
-      <c r="M32" s="15"/>
+    </row>
+    <row r="32" ht="17.25" spans="2:27">
+      <c r="B32" s="14"/>
+      <c r="C32" s="14"/>
+      <c r="D32" s="15"/>
+      <c r="E32" s="15"/>
+      <c r="F32" s="14"/>
+      <c r="G32" s="14"/>
+      <c r="H32" s="18"/>
+      <c r="I32" s="14"/>
+      <c r="J32" s="14"/>
+      <c r="K32" s="14"/>
+      <c r="L32" s="14"/>
+      <c r="M32" s="14"/>
       <c r="N32" s="15"/>
-      <c r="O32" s="16"/>
-    </row>
-    <row r="33" ht="17.25" spans="2:15">
-      <c r="B33" s="15"/>
-      <c r="C33" s="15"/>
-      <c r="D33" s="16"/>
-      <c r="E33" s="16"/>
-      <c r="F33" s="16"/>
-      <c r="G33" s="15"/>
-      <c r="H33" s="15"/>
-      <c r="I33" s="19"/>
-      <c r="J33" s="15"/>
-      <c r="K33" s="15"/>
-      <c r="L33" s="15"/>
-      <c r="M33" s="15"/>
+    </row>
+    <row r="33" ht="17.25" spans="2:14">
+      <c r="B33" s="14"/>
+      <c r="C33" s="14"/>
+      <c r="D33" s="15"/>
+      <c r="E33" s="15"/>
+      <c r="F33" s="14"/>
+      <c r="G33" s="14"/>
+      <c r="H33" s="18"/>
+      <c r="I33" s="14"/>
+      <c r="J33" s="14"/>
+      <c r="K33" s="14"/>
+      <c r="L33" s="14"/>
+      <c r="M33" s="14"/>
       <c r="N33" s="15"/>
-      <c r="O33" s="16"/>
-    </row>
-    <row r="34" ht="17.25" spans="2:15">
-      <c r="B34" s="15"/>
-      <c r="C34" s="15"/>
-      <c r="D34" s="16"/>
-      <c r="E34" s="16"/>
-      <c r="F34" s="16"/>
-      <c r="G34" s="15"/>
-      <c r="H34" s="15"/>
-      <c r="I34" s="19"/>
-      <c r="J34" s="15"/>
-      <c r="K34" s="15"/>
-      <c r="L34" s="15"/>
-      <c r="M34" s="15"/>
+    </row>
+    <row r="34" ht="17.25" spans="2:14">
+      <c r="B34" s="14"/>
+      <c r="C34" s="14"/>
+      <c r="D34" s="15"/>
+      <c r="E34" s="15"/>
+      <c r="F34" s="14"/>
+      <c r="G34" s="14"/>
+      <c r="H34" s="18"/>
+      <c r="I34" s="14"/>
+      <c r="J34" s="14"/>
+      <c r="K34" s="14"/>
+      <c r="L34" s="14"/>
+      <c r="M34" s="14"/>
       <c r="N34" s="15"/>
-      <c r="O34" s="16"/>
-    </row>
-    <row r="35" ht="17.25" spans="2:15">
-      <c r="B35" s="15"/>
-      <c r="C35" s="15"/>
-      <c r="D35" s="16"/>
-      <c r="E35" s="16"/>
-      <c r="F35" s="16"/>
-      <c r="G35" s="15"/>
-      <c r="H35" s="15"/>
-      <c r="I35" s="19"/>
-      <c r="J35" s="15"/>
-      <c r="K35" s="15"/>
-      <c r="L35" s="15"/>
-      <c r="M35" s="15"/>
+    </row>
+    <row r="35" ht="17.25" spans="2:14">
+      <c r="B35" s="14"/>
+      <c r="C35" s="14"/>
+      <c r="D35" s="15"/>
+      <c r="E35" s="15"/>
+      <c r="F35" s="14"/>
+      <c r="G35" s="14"/>
+      <c r="H35" s="18"/>
+      <c r="I35" s="14"/>
+      <c r="J35" s="14"/>
+      <c r="K35" s="14"/>
+      <c r="L35" s="14"/>
+      <c r="M35" s="14"/>
       <c r="N35" s="15"/>
-      <c r="O35" s="16"/>
-    </row>
-    <row r="36" ht="17.25" spans="2:15">
-      <c r="B36" s="15"/>
-      <c r="C36" s="15"/>
-      <c r="D36" s="16"/>
-      <c r="E36" s="16"/>
-      <c r="F36" s="16"/>
-      <c r="G36" s="15"/>
-      <c r="H36" s="15"/>
-      <c r="I36" s="19"/>
-      <c r="J36" s="15"/>
-      <c r="K36" s="15"/>
-      <c r="L36" s="15"/>
-      <c r="M36" s="15"/>
+    </row>
+    <row r="36" ht="17.25" spans="2:14">
+      <c r="B36" s="14"/>
+      <c r="C36" s="14"/>
+      <c r="D36" s="15"/>
+      <c r="E36" s="15"/>
+      <c r="F36" s="14"/>
+      <c r="G36" s="14"/>
+      <c r="H36" s="18"/>
+      <c r="I36" s="14"/>
+      <c r="J36" s="14"/>
+      <c r="K36" s="14"/>
+      <c r="L36" s="14"/>
+      <c r="M36" s="14"/>
       <c r="N36" s="15"/>
-      <c r="O36" s="16"/>
-    </row>
-    <row r="37" ht="17.25" spans="2:15">
-      <c r="B37" s="15"/>
-      <c r="C37" s="15"/>
-      <c r="D37" s="16"/>
-      <c r="E37" s="16"/>
-      <c r="F37" s="16"/>
-      <c r="G37" s="15"/>
-      <c r="H37" s="15"/>
-      <c r="I37" s="19"/>
-      <c r="J37" s="15"/>
-      <c r="K37" s="15"/>
-      <c r="L37" s="15"/>
-      <c r="M37" s="15"/>
+    </row>
+    <row r="37" ht="17.25" spans="2:14">
+      <c r="B37" s="14"/>
+      <c r="C37" s="14"/>
+      <c r="D37" s="15"/>
+      <c r="E37" s="15"/>
+      <c r="F37" s="14"/>
+      <c r="G37" s="14"/>
+      <c r="H37" s="18"/>
+      <c r="I37" s="14"/>
+      <c r="J37" s="14"/>
+      <c r="K37" s="14"/>
+      <c r="L37" s="14"/>
+      <c r="M37" s="14"/>
       <c r="N37" s="15"/>
-      <c r="O37" s="16"/>
-    </row>
-    <row r="38" ht="17.25" spans="2:15">
-      <c r="B38" s="15"/>
-      <c r="C38" s="15"/>
-      <c r="D38" s="16"/>
-      <c r="E38" s="16"/>
-      <c r="F38" s="16"/>
-      <c r="G38" s="15"/>
-      <c r="H38" s="15"/>
-      <c r="I38" s="19"/>
-      <c r="J38" s="15"/>
-      <c r="K38" s="15"/>
-      <c r="L38" s="15"/>
-      <c r="M38" s="15"/>
+    </row>
+    <row r="38" ht="17.25" spans="2:14">
+      <c r="B38" s="14"/>
+      <c r="C38" s="14"/>
+      <c r="D38" s="15"/>
+      <c r="E38" s="15"/>
+      <c r="F38" s="14"/>
+      <c r="G38" s="14"/>
+      <c r="H38" s="18"/>
+      <c r="I38" s="14"/>
+      <c r="J38" s="14"/>
+      <c r="K38" s="14"/>
+      <c r="L38" s="14"/>
+      <c r="M38" s="14"/>
       <c r="N38" s="15"/>
-      <c r="O38" s="16"/>
-    </row>
-    <row r="39" ht="17.25" spans="2:15">
-      <c r="B39" s="15"/>
-      <c r="C39" s="15"/>
-      <c r="D39" s="16"/>
-      <c r="E39" s="16"/>
-      <c r="F39" s="16"/>
-      <c r="G39" s="15"/>
-      <c r="H39" s="15"/>
-      <c r="I39" s="19"/>
-      <c r="J39" s="15"/>
-      <c r="K39" s="15"/>
-      <c r="L39" s="15"/>
-      <c r="M39" s="15"/>
+    </row>
+    <row r="39" ht="17.25" spans="2:14">
+      <c r="B39" s="14"/>
+      <c r="C39" s="14"/>
+      <c r="D39" s="15"/>
+      <c r="E39" s="15"/>
+      <c r="F39" s="14"/>
+      <c r="G39" s="14"/>
+      <c r="H39" s="18"/>
+      <c r="I39" s="14"/>
+      <c r="J39" s="14"/>
+      <c r="K39" s="14"/>
+      <c r="L39" s="14"/>
+      <c r="M39" s="14"/>
       <c r="N39" s="15"/>
-      <c r="O39" s="16"/>
-    </row>
-    <row r="40" ht="17.25" spans="2:15">
-      <c r="B40" s="15"/>
-      <c r="C40" s="15"/>
-      <c r="D40" s="16"/>
-      <c r="E40" s="16"/>
-      <c r="F40" s="16"/>
-      <c r="G40" s="15"/>
-      <c r="H40" s="15"/>
-      <c r="I40" s="19"/>
-      <c r="J40" s="15"/>
-      <c r="K40" s="15"/>
-      <c r="L40" s="15"/>
-      <c r="M40" s="15"/>
+    </row>
+    <row r="40" ht="17.25" spans="2:14">
+      <c r="B40" s="14"/>
+      <c r="C40" s="14"/>
+      <c r="D40" s="15"/>
+      <c r="E40" s="15"/>
+      <c r="F40" s="14"/>
+      <c r="G40" s="14"/>
+      <c r="H40" s="18"/>
+      <c r="I40" s="14"/>
+      <c r="J40" s="14"/>
+      <c r="K40" s="14"/>
+      <c r="L40" s="14"/>
+      <c r="M40" s="14"/>
       <c r="N40" s="15"/>
-      <c r="O40" s="16"/>
-    </row>
-    <row r="41" ht="17.25" spans="2:15">
-      <c r="B41" s="15"/>
-      <c r="C41" s="15"/>
-      <c r="D41" s="16"/>
-      <c r="E41" s="16"/>
-      <c r="F41" s="16"/>
-      <c r="G41" s="15"/>
-      <c r="H41" s="15"/>
-      <c r="I41" s="19"/>
-      <c r="J41" s="15"/>
-      <c r="K41" s="15"/>
-      <c r="L41" s="15"/>
-      <c r="M41" s="15"/>
+    </row>
+    <row r="41" ht="17.25" spans="2:14">
+      <c r="B41" s="14"/>
+      <c r="C41" s="14"/>
+      <c r="D41" s="15"/>
+      <c r="E41" s="15"/>
+      <c r="F41" s="14"/>
+      <c r="G41" s="14"/>
+      <c r="H41" s="18"/>
+      <c r="I41" s="14"/>
+      <c r="J41" s="14"/>
+      <c r="K41" s="14"/>
+      <c r="L41" s="14"/>
+      <c r="M41" s="14"/>
       <c r="N41" s="15"/>
-      <c r="O41" s="16"/>
-    </row>
-    <row r="42" ht="17.25" spans="2:15">
-      <c r="B42" s="15"/>
-      <c r="C42" s="15"/>
-      <c r="D42" s="16"/>
-      <c r="E42" s="16"/>
-      <c r="F42" s="16"/>
-      <c r="G42" s="15"/>
-      <c r="H42" s="15"/>
-      <c r="I42" s="19"/>
-      <c r="J42" s="15"/>
-      <c r="K42" s="15"/>
-      <c r="L42" s="15"/>
-      <c r="M42" s="15"/>
+    </row>
+    <row r="42" ht="17.25" spans="2:14">
+      <c r="B42" s="14"/>
+      <c r="C42" s="14"/>
+      <c r="D42" s="15"/>
+      <c r="E42" s="15"/>
+      <c r="F42" s="14"/>
+      <c r="G42" s="14"/>
+      <c r="H42" s="18"/>
+      <c r="I42" s="14"/>
+      <c r="J42" s="14"/>
+      <c r="K42" s="14"/>
+      <c r="L42" s="14"/>
+      <c r="M42" s="14"/>
       <c r="N42" s="15"/>
-      <c r="O42" s="16"/>
-    </row>
-    <row r="43" ht="17.25" spans="2:15">
-      <c r="B43" s="15"/>
-      <c r="C43" s="15"/>
-      <c r="D43" s="16"/>
-      <c r="E43" s="16"/>
-      <c r="F43" s="16"/>
-      <c r="G43" s="15"/>
-      <c r="H43" s="15"/>
-      <c r="I43" s="19"/>
-      <c r="J43" s="15"/>
-      <c r="K43" s="15"/>
-      <c r="L43" s="15"/>
-      <c r="M43" s="15"/>
+    </row>
+    <row r="43" ht="17.25" spans="2:14">
+      <c r="B43" s="14"/>
+      <c r="C43" s="14"/>
+      <c r="D43" s="15"/>
+      <c r="E43" s="15"/>
+      <c r="F43" s="14"/>
+      <c r="G43" s="14"/>
+      <c r="H43" s="18"/>
+      <c r="I43" s="14"/>
+      <c r="J43" s="14"/>
+      <c r="K43" s="14"/>
+      <c r="L43" s="14"/>
+      <c r="M43" s="14"/>
       <c r="N43" s="15"/>
-      <c r="O43" s="16"/>
-    </row>
-    <row r="44" ht="17.25" spans="2:15">
-      <c r="B44" s="15"/>
-      <c r="C44" s="15"/>
-      <c r="D44" s="16"/>
-      <c r="E44" s="16"/>
-      <c r="F44" s="16"/>
-      <c r="G44" s="15"/>
-      <c r="H44" s="15"/>
-      <c r="I44" s="19"/>
-      <c r="J44" s="15"/>
-      <c r="K44" s="15"/>
-      <c r="L44" s="15"/>
-      <c r="M44" s="15"/>
+    </row>
+    <row r="44" ht="17.25" spans="2:14">
+      <c r="B44" s="14"/>
+      <c r="C44" s="14"/>
+      <c r="D44" s="15"/>
+      <c r="E44" s="15"/>
+      <c r="F44" s="14"/>
+      <c r="G44" s="14"/>
+      <c r="H44" s="18"/>
+      <c r="I44" s="14"/>
+      <c r="J44" s="14"/>
+      <c r="K44" s="14"/>
+      <c r="L44" s="14"/>
+      <c r="M44" s="14"/>
       <c r="N44" s="15"/>
-      <c r="O44" s="16"/>
-    </row>
-    <row r="45" ht="17.25" spans="2:15">
-      <c r="B45" s="15"/>
-      <c r="C45" s="15"/>
-      <c r="D45" s="16"/>
-      <c r="E45" s="16"/>
-      <c r="F45" s="16"/>
-      <c r="G45" s="15"/>
-      <c r="H45" s="15"/>
-      <c r="I45" s="19"/>
-      <c r="J45" s="15"/>
-      <c r="K45" s="15"/>
-      <c r="L45" s="15"/>
-      <c r="M45" s="15"/>
+    </row>
+    <row r="45" ht="17.25" spans="2:14">
+      <c r="B45" s="14"/>
+      <c r="C45" s="14"/>
+      <c r="D45" s="15"/>
+      <c r="E45" s="15"/>
+      <c r="F45" s="14"/>
+      <c r="G45" s="14"/>
+      <c r="H45" s="18"/>
+      <c r="I45" s="14"/>
+      <c r="J45" s="14"/>
+      <c r="K45" s="14"/>
+      <c r="L45" s="14"/>
+      <c r="M45" s="14"/>
       <c r="N45" s="15"/>
-      <c r="O45" s="16"/>
-    </row>
-    <row r="46" ht="17.25" spans="2:15">
-      <c r="B46" s="15"/>
-      <c r="C46" s="15"/>
-      <c r="D46" s="16"/>
-      <c r="E46" s="16"/>
-      <c r="F46" s="16"/>
-      <c r="G46" s="15"/>
-      <c r="H46" s="15"/>
-      <c r="I46" s="19"/>
-      <c r="J46" s="15"/>
-      <c r="K46" s="15"/>
-      <c r="L46" s="15"/>
-      <c r="M46" s="15"/>
+    </row>
+    <row r="46" ht="17.25" spans="2:14">
+      <c r="B46" s="14"/>
+      <c r="C46" s="14"/>
+      <c r="D46" s="15"/>
+      <c r="E46" s="15"/>
+      <c r="F46" s="14"/>
+      <c r="G46" s="14"/>
+      <c r="H46" s="18"/>
+      <c r="I46" s="14"/>
+      <c r="J46" s="14"/>
+      <c r="K46" s="14"/>
+      <c r="L46" s="14"/>
+      <c r="M46" s="14"/>
       <c r="N46" s="15"/>
-      <c r="O46" s="16"/>
-    </row>
-    <row r="47" ht="17.25" spans="2:15">
-      <c r="B47" s="15"/>
-      <c r="C47" s="15"/>
-      <c r="D47" s="16"/>
-      <c r="E47" s="16"/>
-      <c r="F47" s="16"/>
-      <c r="G47" s="15"/>
-      <c r="H47" s="15"/>
-      <c r="I47" s="19"/>
-      <c r="J47" s="15"/>
-      <c r="K47" s="15"/>
-      <c r="L47" s="15"/>
-      <c r="M47" s="15"/>
+    </row>
+    <row r="47" ht="17.25" spans="2:14">
+      <c r="B47" s="14"/>
+      <c r="C47" s="14"/>
+      <c r="D47" s="15"/>
+      <c r="E47" s="15"/>
+      <c r="F47" s="14"/>
+      <c r="G47" s="14"/>
+      <c r="H47" s="18"/>
+      <c r="I47" s="14"/>
+      <c r="J47" s="14"/>
+      <c r="K47" s="14"/>
+      <c r="L47" s="14"/>
+      <c r="M47" s="14"/>
       <c r="N47" s="15"/>
-      <c r="O47" s="16"/>
-    </row>
-    <row r="48" ht="17.25" spans="2:15">
-      <c r="B48" s="15"/>
-      <c r="C48" s="15"/>
-      <c r="D48" s="16"/>
-      <c r="E48" s="16"/>
-      <c r="F48" s="16"/>
-      <c r="G48" s="15"/>
-      <c r="H48" s="15"/>
-      <c r="I48" s="19"/>
-      <c r="J48" s="15"/>
-      <c r="K48" s="15"/>
-      <c r="L48" s="15"/>
-      <c r="M48" s="15"/>
+    </row>
+    <row r="48" ht="17.25" spans="2:14">
+      <c r="B48" s="14"/>
+      <c r="C48" s="14"/>
+      <c r="D48" s="15"/>
+      <c r="E48" s="15"/>
+      <c r="F48" s="14"/>
+      <c r="G48" s="14"/>
+      <c r="H48" s="18"/>
+      <c r="I48" s="14"/>
+      <c r="J48" s="14"/>
+      <c r="K48" s="14"/>
+      <c r="L48" s="14"/>
+      <c r="M48" s="14"/>
       <c r="N48" s="15"/>
-      <c r="O48" s="16"/>
-    </row>
-    <row r="49" ht="17.25" spans="2:15">
-      <c r="B49" s="15"/>
-      <c r="C49" s="15"/>
-      <c r="D49" s="16"/>
-      <c r="E49" s="16"/>
-      <c r="F49" s="16"/>
-      <c r="G49" s="15"/>
-      <c r="H49" s="15"/>
-      <c r="I49" s="19"/>
-      <c r="J49" s="15"/>
-      <c r="K49" s="15"/>
-      <c r="L49" s="15"/>
-      <c r="M49" s="15"/>
+    </row>
+    <row r="49" ht="17.25" spans="2:14">
+      <c r="B49" s="14"/>
+      <c r="C49" s="14"/>
+      <c r="D49" s="15"/>
+      <c r="E49" s="15"/>
+      <c r="F49" s="14"/>
+      <c r="G49" s="14"/>
+      <c r="H49" s="18"/>
+      <c r="I49" s="14"/>
+      <c r="J49" s="14"/>
+      <c r="K49" s="14"/>
+      <c r="L49" s="14"/>
+      <c r="M49" s="14"/>
       <c r="N49" s="15"/>
-      <c r="O49" s="16"/>
-    </row>
-    <row r="50" ht="17.25" spans="2:15">
-      <c r="B50" s="15"/>
-      <c r="C50" s="15"/>
-      <c r="D50" s="16"/>
-      <c r="E50" s="16"/>
-      <c r="F50" s="16"/>
-      <c r="G50" s="15"/>
-      <c r="H50" s="15"/>
-      <c r="I50" s="19"/>
-      <c r="J50" s="15"/>
-      <c r="K50" s="15"/>
-      <c r="L50" s="15"/>
-      <c r="M50" s="15"/>
+    </row>
+    <row r="50" ht="17.25" spans="2:14">
+      <c r="B50" s="14"/>
+      <c r="C50" s="14"/>
+      <c r="D50" s="15"/>
+      <c r="E50" s="15"/>
+      <c r="F50" s="14"/>
+      <c r="G50" s="14"/>
+      <c r="H50" s="18"/>
+      <c r="I50" s="14"/>
+      <c r="J50" s="14"/>
+      <c r="K50" s="14"/>
+      <c r="L50" s="14"/>
+      <c r="M50" s="14"/>
       <c r="N50" s="15"/>
-      <c r="O50" s="16"/>
-    </row>
-    <row r="51" ht="17.25" spans="2:15">
-      <c r="B51" s="15"/>
-      <c r="C51" s="15"/>
-      <c r="D51" s="16"/>
-      <c r="E51" s="16"/>
-      <c r="F51" s="16"/>
-      <c r="G51" s="15"/>
-      <c r="H51" s="15"/>
-      <c r="I51" s="19"/>
-      <c r="J51" s="15"/>
-      <c r="K51" s="15"/>
-      <c r="L51" s="15"/>
-      <c r="M51" s="15"/>
+    </row>
+    <row r="51" ht="17.25" spans="2:14">
+      <c r="B51" s="14"/>
+      <c r="C51" s="14"/>
+      <c r="D51" s="15"/>
+      <c r="E51" s="15"/>
+      <c r="F51" s="14"/>
+      <c r="G51" s="14"/>
+      <c r="H51" s="18"/>
+      <c r="I51" s="14"/>
+      <c r="J51" s="14"/>
+      <c r="K51" s="14"/>
+      <c r="L51" s="14"/>
+      <c r="M51" s="14"/>
       <c r="N51" s="15"/>
-      <c r="O51" s="16"/>
-    </row>
-    <row r="52" ht="17.25" spans="2:15">
-      <c r="B52" s="15"/>
-      <c r="C52" s="15"/>
-      <c r="D52" s="16"/>
-      <c r="E52" s="16"/>
-      <c r="F52" s="16"/>
-      <c r="G52" s="15"/>
-      <c r="H52" s="15"/>
-      <c r="I52" s="19"/>
-      <c r="J52" s="15"/>
-      <c r="K52" s="15"/>
-      <c r="L52" s="15"/>
-      <c r="M52" s="15"/>
+    </row>
+    <row r="52" ht="17.25" spans="2:14">
+      <c r="B52" s="14"/>
+      <c r="C52" s="14"/>
+      <c r="D52" s="15"/>
+      <c r="E52" s="15"/>
+      <c r="F52" s="14"/>
+      <c r="G52" s="14"/>
+      <c r="H52" s="18"/>
+      <c r="I52" s="14"/>
+      <c r="J52" s="14"/>
+      <c r="K52" s="14"/>
+      <c r="L52" s="14"/>
+      <c r="M52" s="14"/>
       <c r="N52" s="15"/>
-      <c r="O52" s="16"/>
-    </row>
-    <row r="53" ht="17.25" spans="2:15">
-      <c r="B53" s="15"/>
-      <c r="C53" s="15"/>
-      <c r="D53" s="16"/>
-      <c r="E53" s="16"/>
-      <c r="F53" s="16"/>
-      <c r="G53" s="15"/>
-      <c r="H53" s="15"/>
-      <c r="I53" s="19"/>
-      <c r="J53" s="15"/>
-      <c r="K53" s="15"/>
-      <c r="L53" s="15"/>
-      <c r="M53" s="15"/>
+    </row>
+    <row r="53" ht="17.25" spans="2:14">
+      <c r="B53" s="14"/>
+      <c r="C53" s="14"/>
+      <c r="D53" s="15"/>
+      <c r="E53" s="15"/>
+      <c r="F53" s="14"/>
+      <c r="G53" s="14"/>
+      <c r="H53" s="18"/>
+      <c r="I53" s="14"/>
+      <c r="J53" s="14"/>
+      <c r="K53" s="14"/>
+      <c r="L53" s="14"/>
+      <c r="M53" s="14"/>
       <c r="N53" s="15"/>
-      <c r="O53" s="16"/>
-    </row>
-    <row r="54" ht="17.25" spans="2:15">
-      <c r="B54" s="15"/>
-      <c r="C54" s="15"/>
-      <c r="D54" s="16"/>
-      <c r="E54" s="16"/>
-      <c r="F54" s="16"/>
-      <c r="G54" s="15"/>
-      <c r="H54" s="15"/>
-      <c r="I54" s="19"/>
-      <c r="J54" s="15"/>
-      <c r="K54" s="15"/>
-      <c r="L54" s="15"/>
-      <c r="M54" s="15"/>
+    </row>
+    <row r="54" ht="17.25" spans="2:14">
+      <c r="B54" s="14"/>
+      <c r="C54" s="14"/>
+      <c r="D54" s="15"/>
+      <c r="E54" s="15"/>
+      <c r="F54" s="14"/>
+      <c r="G54" s="14"/>
+      <c r="H54" s="18"/>
+      <c r="I54" s="14"/>
+      <c r="J54" s="14"/>
+      <c r="K54" s="14"/>
+      <c r="L54" s="14"/>
+      <c r="M54" s="14"/>
       <c r="N54" s="15"/>
-      <c r="O54" s="16"/>
-    </row>
-    <row r="55" ht="17.25" spans="2:15">
-      <c r="B55" s="15"/>
-      <c r="C55" s="15"/>
-      <c r="D55" s="16"/>
-      <c r="E55" s="16"/>
-      <c r="F55" s="16"/>
-      <c r="G55" s="15"/>
-      <c r="H55" s="15"/>
-      <c r="I55" s="19"/>
-      <c r="J55" s="15"/>
-      <c r="K55" s="15"/>
-      <c r="L55" s="15"/>
-      <c r="M55" s="15"/>
+    </row>
+    <row r="55" ht="17.25" spans="2:14">
+      <c r="B55" s="14"/>
+      <c r="C55" s="14"/>
+      <c r="D55" s="15"/>
+      <c r="E55" s="15"/>
+      <c r="F55" s="14"/>
+      <c r="G55" s="14"/>
+      <c r="H55" s="18"/>
+      <c r="I55" s="14"/>
+      <c r="J55" s="14"/>
+      <c r="K55" s="14"/>
+      <c r="L55" s="14"/>
+      <c r="M55" s="14"/>
       <c r="N55" s="15"/>
-      <c r="O55" s="16"/>
-    </row>
-    <row r="56" ht="17.25" spans="2:15">
-      <c r="B56" s="15"/>
-      <c r="C56" s="15"/>
-      <c r="D56" s="16"/>
-      <c r="E56" s="16"/>
-      <c r="F56" s="16"/>
-      <c r="G56" s="15"/>
-      <c r="H56" s="15"/>
-      <c r="I56" s="19"/>
-      <c r="J56" s="15"/>
-      <c r="K56" s="15"/>
-      <c r="L56" s="15"/>
-      <c r="M56" s="15"/>
+    </row>
+    <row r="56" ht="17.25" spans="2:14">
+      <c r="B56" s="14"/>
+      <c r="C56" s="14"/>
+      <c r="D56" s="15"/>
+      <c r="E56" s="15"/>
+      <c r="F56" s="14"/>
+      <c r="G56" s="14"/>
+      <c r="H56" s="18"/>
+      <c r="I56" s="14"/>
+      <c r="J56" s="14"/>
+      <c r="K56" s="14"/>
+      <c r="L56" s="14"/>
+      <c r="M56" s="14"/>
       <c r="N56" s="15"/>
-      <c r="O56" s="16"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="I8">
+  <conditionalFormatting sqref="H8">
     <cfRule type="expression" dxfId="0" priority="1">
-      <formula>AND(SUMPRODUCT(IFERROR(1*(($I$8&amp;"x")=(I8&amp;"x")),0))&gt;1,NOT(ISBLANK(I8)))</formula>
+      <formula>AND(SUMPRODUCT(IFERROR(1*(($H$8&amp;"x")=(H8&amp;"x")),0))&gt;1,NOT(ISBLANK(H8)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K9">
+  <conditionalFormatting sqref="J9">
     <cfRule type="expression" dxfId="0" priority="6">
-      <formula>AND(SUMPRODUCT(IFERROR(1*(($K$9&amp;"x")=(K9&amp;"x")),0))&gt;1,NOT(ISBLANK(K9)))</formula>
+      <formula>AND(SUMPRODUCT(IFERROR(1*(($J$9&amp;"x")=(J9&amp;"x")),0))&gt;1,NOT(ISBLANK(J9)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K10">
+  <conditionalFormatting sqref="J10">
     <cfRule type="expression" dxfId="0" priority="5">
-      <formula>AND(SUMPRODUCT(IFERROR(1*(($K$10&amp;"x")=(K10&amp;"x")),0))&gt;1,NOT(ISBLANK(K10)))</formula>
+      <formula>AND(SUMPRODUCT(IFERROR(1*(($J$10&amp;"x")=(J10&amp;"x")),0))&gt;1,NOT(ISBLANK(J10)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B7:B8 B10:B11">
@@ -2711,9 +2620,9 @@
       <formula>AND(SUMPRODUCT(IFERROR(1*(($B$7:$B$8&amp;"x")=(B7&amp;"x")),0))+SUMPRODUCT(IFERROR(1*(($B$10:$B$11&amp;"x")=(B7&amp;"x")),0))&gt;1,NOT(ISBLANK(B7)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I7 I9">
+  <conditionalFormatting sqref="H7 H9">
     <cfRule type="expression" dxfId="0" priority="2">
-      <formula>AND(SUMPRODUCT(IFERROR(1*(($I$7&amp;"x")=(I7&amp;"x")),0))+SUMPRODUCT(IFERROR(1*(($I$9&amp;"x")=(I7&amp;"x")),0))&gt;1,NOT(ISBLANK(I7)))</formula>
+      <formula>AND(SUMPRODUCT(IFERROR(1*(($H$7&amp;"x")=(H7&amp;"x")),0))+SUMPRODUCT(IFERROR(1*(($H$9&amp;"x")=(H7&amp;"x")),0))&gt;1,NOT(ISBLANK(H7)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B9 B12">
